--- a/artfynd/A 52647-2023 artfynd.xlsx
+++ b/artfynd/A 52647-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117455530</v>
+        <v>117725883</v>
       </c>
       <c r="B2" t="n">
-        <v>79563</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Rönnöfors SÖ, Jmt</t>
+          <t>Långnäsudden, Långnäsudden, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>446195</v>
+        <v>446406</v>
       </c>
       <c r="R2" t="n">
-        <v>7055248</v>
+        <v>7055263</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-05-30</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-05-30</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,27 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117455534</v>
+        <v>117721232</v>
       </c>
       <c r="B3" t="n">
-        <v>79563</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80298</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,37 +783,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>388</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Rönnöfors SÖ, Jmt</t>
+          <t>Långnäsudden, Långnäsudden, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>446283</v>
+        <v>446496</v>
       </c>
       <c r="R3" t="n">
-        <v>7055547</v>
+        <v>7055277</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -847,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-05-30</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-05-30</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,12 +857,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -882,12 +872,7 @@
         <v>117455551</v>
       </c>
       <c r="B4" t="n">
-        <v>86818</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,53 +966,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117455550</v>
+        <v>117722968</v>
       </c>
       <c r="B5" t="n">
-        <v>91066</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>760</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Rönnöfors SÖ, Jmt</t>
+          <t>Stenmyren, Stenmyren, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>446518</v>
+        <v>446089</v>
       </c>
       <c r="R5" t="n">
-        <v>7055241</v>
+        <v>7055375</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1051,12 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-05-30</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-05-30</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1071,49 +1051,44 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117455544</v>
+        <v>117455550</v>
       </c>
       <c r="B6" t="n">
-        <v>90519</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92509</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>760</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>446225</v>
+        <v>446518</v>
       </c>
       <c r="R6" t="n">
-        <v>7054982</v>
+        <v>7055241</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,53 +1160,51 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117455545</v>
+        <v>117723270</v>
       </c>
       <c r="B7" t="n">
-        <v>90519</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92605</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>898</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Rönnöfors SÖ, Jmt</t>
+          <t>Långnäsudden, Långnäsudden, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>446348</v>
+        <v>446209</v>
       </c>
       <c r="R7" t="n">
-        <v>7055482</v>
+        <v>7055455</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1255,12 +1228,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-05-30</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-05-30</t>
+          <t>2024-06-12</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Relativt klen men gammal och kraftigt murken låga, förrötad av bl.a. ullticka.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1269,33 +1247,29 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117455466</v>
+        <v>117724120</v>
       </c>
       <c r="B8" t="n">
-        <v>57290</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1303,37 +1277,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Rönnöfors SÖ, Jmt</t>
+          <t>Långnäsudden, Långnäsudden, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>446227</v>
+        <v>446443</v>
       </c>
       <c r="R8" t="n">
-        <v>7055293</v>
+        <v>7055375</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1357,17 +1331,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-05-30</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-05-30</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1382,27 +1351,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117455465</v>
+        <v>117721764</v>
       </c>
       <c r="B9" t="n">
-        <v>57290</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1410,37 +1374,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Rönnöfors SÖ, Jmt</t>
+          <t>Bodberget, Bodberget, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>446350</v>
+        <v>446147</v>
       </c>
       <c r="R9" t="n">
-        <v>7055479</v>
+        <v>7055135</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1464,24 +1428,19 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-05-30</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-05-30</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Gammalt bohål</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="b">
         <v>0</v>
@@ -1489,27 +1448,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117455475</v>
+        <v>117722567</v>
       </c>
       <c r="B10" t="n">
-        <v>57290</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1517,37 +1471,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Rönnöfors SÖ, Jmt</t>
+          <t>Stenmyren, Stenmyren, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>446291</v>
+        <v>446009</v>
       </c>
       <c r="R10" t="n">
-        <v>7055557</v>
+        <v>7055165</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1571,17 +1525,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-05-30</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-05-30</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1596,27 +1545,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117455471</v>
+        <v>117722938</v>
       </c>
       <c r="B11" t="n">
-        <v>57290</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1624,37 +1568,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Rönnöfors SÖ, Jmt</t>
+          <t>Stenmyren, Stenmyren, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>446543</v>
+        <v>446089</v>
       </c>
       <c r="R11" t="n">
-        <v>7055148</v>
+        <v>7055375</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1678,17 +1622,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-05-30</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-05-30</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1703,62 +1642,57 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117722938</v>
+        <v>117724681</v>
       </c>
       <c r="B12" t="n">
-        <v>90945</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1209</v>
+        <v>1467</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Stenmyren (Stenmyren), Jmt</t>
+          <t>Bodberget, Bodberget, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>446089</v>
+        <v>446171</v>
       </c>
       <c r="R12" t="n">
-        <v>7055375</v>
+        <v>7055005</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1817,15 +1751,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117722968</v>
+        <v>117725887</v>
       </c>
       <c r="B13" t="n">
-        <v>90786</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1833,34 +1762,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>1467</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Stenmyren (Stenmyren), Jmt</t>
+          <t>Långnäsudden, Långnäsudden, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>446089</v>
+        <v>446406</v>
       </c>
       <c r="R13" t="n">
-        <v>7055375</v>
+        <v>7055263</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1901,8 +1833,19 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>Björkhögstubbe</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Björkhögstubbe</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -1919,15 +1862,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117721356</v>
+        <v>117724086</v>
       </c>
       <c r="B14" t="n">
-        <v>74596</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92097</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1935,37 +1873,40 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6440</v>
+        <v>1588</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Långnäsudden (Långnäsudden), Jmt</t>
+          <t>Kävåsen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>446427</v>
+        <v>446438</v>
       </c>
       <c r="R14" t="n">
-        <v>7055266</v>
+        <v>7055141</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2003,6 +1944,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2021,50 +1963,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117725883</v>
+        <v>117721769</v>
       </c>
       <c r="B15" t="n">
-        <v>74588</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92281</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>308</v>
+        <v>2062</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Långnäsudden (Långnäsudden), Jmt</t>
+          <t>Bodberget, Bodberget, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>446406</v>
+        <v>446147</v>
       </c>
       <c r="R15" t="n">
-        <v>7055263</v>
+        <v>7055135</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2123,50 +2060,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117724681</v>
+        <v>117726009</v>
       </c>
       <c r="B16" t="n">
-        <v>74601</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83290</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1467</v>
+        <v>6439</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Bodberget (Bodberget), Jmt</t>
+          <t>Långnäsudden, Långnäsudden, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>446171</v>
+        <v>446406</v>
       </c>
       <c r="R16" t="n">
-        <v>7055005</v>
+        <v>7055263</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2225,15 +2157,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117721232</v>
+        <v>117721356</v>
       </c>
       <c r="B17" t="n">
-        <v>79431</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2241,34 +2168,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>388</v>
+        <v>6440</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Långnäsudden (Långnäsudden), Jmt</t>
+          <t>Långnäsudden, Långnäsudden, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>446496</v>
+        <v>446427</v>
       </c>
       <c r="R17" t="n">
-        <v>7055277</v>
+        <v>7055266</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2327,15 +2254,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117725887</v>
+        <v>117455530</v>
       </c>
       <c r="B18" t="n">
-        <v>74601</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2343,40 +2265,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1467</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Långnäsudden (Långnäsudden), Jmt</t>
+          <t>Rönnöfors SÖ, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>446406</v>
+        <v>446195</v>
       </c>
       <c r="R18" t="n">
-        <v>7055263</v>
+        <v>7055248</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2400,12 +2319,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2414,82 +2333,66 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AL18" t="inlineStr">
-        <is>
-          <t>Björkhögstubbe</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Björkhögstubbe</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117722567</v>
+        <v>117455534</v>
       </c>
       <c r="B19" t="n">
-        <v>90945</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Stenmyren (Stenmyren), Jmt</t>
+          <t>Rönnöfors SÖ, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>446009</v>
+        <v>446283</v>
       </c>
       <c r="R19" t="n">
-        <v>7055165</v>
+        <v>7055547</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2513,12 +2416,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2533,65 +2436,60 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117721769</v>
+        <v>117455465</v>
       </c>
       <c r="B20" t="n">
-        <v>90845</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2062</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bodberget (Bodberget), Jmt</t>
+          <t>Rönnöfors SÖ, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>446147</v>
+        <v>446350</v>
       </c>
       <c r="R20" t="n">
-        <v>7055135</v>
+        <v>7055479</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2615,19 +2513,24 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-05-30</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Gammalt bohål</t>
         </is>
       </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG20" t="b">
         <v>0</v>
@@ -2635,27 +2538,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117721354</v>
+        <v>117455466</v>
       </c>
       <c r="B21" t="n">
-        <v>77421</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2663,37 +2561,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Långnäsudden (Långnäsudden), Jmt</t>
+          <t>Rönnöfors SÖ, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>446427</v>
+        <v>446227</v>
       </c>
       <c r="R21" t="n">
-        <v>7055266</v>
+        <v>7055293</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2717,12 +2615,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-05-30</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2737,65 +2640,60 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117726009</v>
+        <v>117455471</v>
       </c>
       <c r="B22" t="n">
-        <v>74580</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6439</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Långnäsudden (Långnäsudden), Jmt</t>
+          <t>Rönnöfors SÖ, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>446406</v>
+        <v>446543</v>
       </c>
       <c r="R22" t="n">
-        <v>7055263</v>
+        <v>7055148</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2819,12 +2717,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-05-30</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2839,68 +2742,60 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>117723270</v>
+        <v>117455472</v>
       </c>
       <c r="B23" t="n">
-        <v>91168</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>898</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Långnäsudden (Långnäsudden), Jmt</t>
+          <t>Rönnöfors SÖ, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>446209</v>
+        <v>446345</v>
       </c>
       <c r="R23" t="n">
-        <v>7055455</v>
+        <v>7055524</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2924,17 +2819,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Relativt klen men gammal och kraftigt murken låga, förrötad av bl.a. ullticka.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2943,34 +2838,28 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>117721764</v>
+        <v>117455473</v>
       </c>
       <c r="B24" t="n">
-        <v>90503</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2978,37 +2867,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Bodberget (Bodberget), Jmt</t>
+          <t>Rönnöfors SÖ, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>446147</v>
+        <v>446326</v>
       </c>
       <c r="R24" t="n">
-        <v>7055135</v>
+        <v>7055543</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3032,12 +2921,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-05-30</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3052,27 +2946,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>117724086</v>
+        <v>117455475</v>
       </c>
       <c r="B25" t="n">
-        <v>90666</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3080,40 +2969,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1588</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Kävåsen, Jmt</t>
+          <t>Rönnöfors SÖ, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>446438</v>
+        <v>446291</v>
       </c>
       <c r="R25" t="n">
-        <v>7055141</v>
+        <v>7055557</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3137,12 +3023,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-05-30</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3151,22 +3042,220 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>117455476</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Rönnöfors SÖ, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>446299</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7055582</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-05-30</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-05-30</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>117721354</v>
+      </c>
+      <c r="B27" t="n">
+        <v>78339</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>228579</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Långnäsudden, Långnäsudden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>446427</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7055266</v>
+      </c>
+      <c r="S27" t="n">
+        <v>20</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-06-12</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-06-12</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
           <t>Rashid Kadhim</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
+      <c r="AX27" t="inlineStr">
         <is>
           <t>Rashid Kadhim</t>
         </is>
       </c>
-      <c r="AY25" t="inlineStr"/>
+      <c r="AY27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 52647-2023 artfynd.xlsx
+++ b/artfynd/A 52647-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AZ27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117725883</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117721232</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117455551</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117722968</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117455550</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1263,6 +1293,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117723270</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1360,6 +1395,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117724120</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1457,6 +1497,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117721764</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1554,6 +1599,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117722567</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1651,6 +1701,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117722938</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1748,6 +1803,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117724681</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1859,6 +1919,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117725887</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1960,6 +2025,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117724086</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2057,6 +2127,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117721769</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2154,6 +2229,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117726009</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2251,6 +2331,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117721356</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2348,6 +2433,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117455530</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2445,6 +2535,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117455534</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2547,6 +2642,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117455465</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2649,6 +2749,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117455466</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2751,6 +2856,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117455471</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2853,6 +2963,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117455472</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2955,6 +3070,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117455473</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3057,6 +3177,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117455475</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3159,6 +3284,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117455476</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3256,8 +3386,41 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117721354</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>